--- a/output/Tables/2019/HIA_per_disease_Rubin.xlsx
+++ b/output/Tables/2019/HIA_per_disease_Rubin.xlsx
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>58494.288</v>
+        <v>58925.169</v>
       </c>
       <c r="C2">
-        <v>55613.417</v>
+        <v>55995.747</v>
       </c>
       <c r="D2">
-        <v>61375.159</v>
+        <v>61854.592</v>
       </c>
       <c r="E2">
-        <v>604892.097</v>
+        <v>606959.8050000001</v>
       </c>
       <c r="F2">
-        <v>587055.503</v>
+        <v>588962.262</v>
       </c>
       <c r="G2">
-        <v>622728.692</v>
+        <v>624957.348</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>80450648928.94099</v>
+        <v>80725654035.556</v>
       </c>
       <c r="L2">
-        <v>78078381883.617</v>
+        <v>78331980839.765</v>
       </c>
       <c r="M2">
-        <v>82822915974.26401</v>
+        <v>83119327231.34801</v>
       </c>
     </row>
     <row r="3">
@@ -471,40 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>40151.634</v>
+        <v>40691.563</v>
       </c>
       <c r="C3">
-        <v>38400.342</v>
+        <v>38919.739</v>
       </c>
       <c r="D3">
-        <v>41902.927</v>
+        <v>42463.387</v>
       </c>
       <c r="E3">
-        <v>35944.137</v>
+        <v>36292.19</v>
       </c>
       <c r="F3">
-        <v>34526.475</v>
+        <v>34859.598</v>
       </c>
       <c r="G3">
-        <v>37361.799</v>
+        <v>37724.783</v>
       </c>
       <c r="H3">
-        <v>2236526326.502</v>
+        <v>2266601445.039</v>
       </c>
       <c r="I3">
-        <v>2138975836.899</v>
+        <v>2167907322.714</v>
       </c>
       <c r="J3">
-        <v>2334076816.105</v>
+        <v>2365295567.364</v>
       </c>
       <c r="K3">
-        <v>4780570189.285</v>
+        <v>4826861303.836</v>
       </c>
       <c r="L3">
-        <v>4592021177.518</v>
+        <v>4636326518.17</v>
       </c>
       <c r="M3">
-        <v>4969119201.052</v>
+        <v>5017396089.503</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>31236.759</v>
+        <v>30229.519</v>
       </c>
       <c r="C4">
-        <v>29749.866</v>
+        <v>28895.149</v>
       </c>
       <c r="D4">
-        <v>32723.653</v>
+        <v>31563.89</v>
       </c>
       <c r="E4">
-        <v>47101.692</v>
+        <v>45478.511</v>
       </c>
       <c r="F4">
-        <v>44355.301</v>
+        <v>43018.981</v>
       </c>
       <c r="G4">
-        <v>49848.083</v>
+        <v>47938.04</v>
       </c>
       <c r="H4">
-        <v>462522697.682</v>
+        <v>447608494.82</v>
       </c>
       <c r="I4">
-        <v>440506268.072</v>
+        <v>427850468.752</v>
       </c>
       <c r="J4">
-        <v>484539127.293</v>
+        <v>467366520.888</v>
       </c>
       <c r="K4">
-        <v>6264525079.272</v>
+        <v>6048641946.477</v>
       </c>
       <c r="L4">
-        <v>5899255086.525</v>
+        <v>5721524533.314</v>
       </c>
       <c r="M4">
-        <v>6629795072.019</v>
+        <v>6375759359.639</v>
       </c>
     </row>
     <row r="5">
@@ -557,40 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>6404.958</v>
+        <v>6467.869</v>
       </c>
       <c r="C5">
-        <v>6093.188</v>
+        <v>6182.283</v>
       </c>
       <c r="D5">
-        <v>6716.728</v>
+        <v>6753.455</v>
       </c>
       <c r="E5">
-        <v>12504.519</v>
+        <v>12608.979</v>
       </c>
       <c r="F5">
-        <v>11870.199</v>
+        <v>12026.415</v>
       </c>
       <c r="G5">
-        <v>13138.839</v>
+        <v>13191.543</v>
       </c>
       <c r="H5">
-        <v>481659263.373</v>
+        <v>486390218.76</v>
       </c>
       <c r="I5">
-        <v>458213842.177</v>
+        <v>464913885.774</v>
       </c>
       <c r="J5">
-        <v>505104684.568</v>
+        <v>507866551.745</v>
       </c>
       <c r="K5">
-        <v>1663101048.418</v>
+        <v>1676994188.187</v>
       </c>
       <c r="L5">
-        <v>1578736472.331</v>
+        <v>1599513135.914</v>
       </c>
       <c r="M5">
-        <v>1747465624.505</v>
+        <v>1754475240.461</v>
       </c>
     </row>
     <row r="6">
@@ -600,40 +600,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>13935.46</v>
+        <v>13944.428</v>
       </c>
       <c r="C6">
-        <v>13088.821</v>
+        <v>13098.584</v>
       </c>
       <c r="D6">
-        <v>14782.1</v>
+        <v>14790.271</v>
       </c>
       <c r="E6">
-        <v>23252.58</v>
+        <v>23366.857</v>
       </c>
       <c r="F6">
-        <v>22098.172</v>
+        <v>22207.806</v>
       </c>
       <c r="G6">
-        <v>24406.988</v>
+        <v>24525.908</v>
       </c>
       <c r="H6">
-        <v>234659214.651</v>
+        <v>234810214.686</v>
       </c>
       <c r="I6">
-        <v>220402650.514</v>
+        <v>220567058.958</v>
       </c>
       <c r="J6">
-        <v>248915778.788</v>
+        <v>249053370.415</v>
       </c>
       <c r="K6">
-        <v>3092593143.733</v>
+        <v>3107791970.082</v>
       </c>
       <c r="L6">
-        <v>2939056873.721</v>
+        <v>2953638210.103</v>
       </c>
       <c r="M6">
-        <v>3246129413.745</v>
+        <v>3261945730.061</v>
       </c>
     </row>
     <row r="7">
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>126008.848</v>
+        <v>143999.772</v>
       </c>
       <c r="C7">
-        <v>121264.534</v>
+        <v>138613.556</v>
       </c>
       <c r="D7">
-        <v>130753.163</v>
+        <v>149385.988</v>
       </c>
       <c r="E7">
-        <v>41036.118</v>
+        <v>46479.568</v>
       </c>
       <c r="F7">
-        <v>38886.047</v>
+        <v>44069.496</v>
       </c>
       <c r="G7">
-        <v>43186.189</v>
+        <v>48889.639</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -670,13 +670,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>5457803706.637</v>
+        <v>6181782487.624</v>
       </c>
       <c r="L7">
-        <v>5171844281.957</v>
+        <v>5861242956.497</v>
       </c>
       <c r="M7">
-        <v>5743763131.317</v>
+        <v>6502322018.75</v>
       </c>
     </row>
     <row r="8">
@@ -686,40 +686,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>217737.659</v>
+        <v>235333.151</v>
       </c>
       <c r="C8">
-        <v>208596.751</v>
+        <v>225709.311</v>
       </c>
       <c r="D8">
-        <v>226878.571</v>
+        <v>244956.991</v>
       </c>
       <c r="E8">
-        <v>159839.046</v>
+        <v>164226.105</v>
       </c>
       <c r="F8">
-        <v>151736.194</v>
+        <v>156182.296</v>
       </c>
       <c r="G8">
-        <v>167941.898</v>
+        <v>172269.913</v>
       </c>
       <c r="H8">
-        <v>3415367502.208</v>
+        <v>3435410373.305</v>
       </c>
       <c r="I8">
-        <v>3258098597.662</v>
+        <v>3281238736.198</v>
       </c>
       <c r="J8">
-        <v>3572636406.754</v>
+        <v>3589582010.412</v>
       </c>
       <c r="K8">
-        <v>21258593167.345</v>
+        <v>21842071896.206</v>
       </c>
       <c r="L8">
-        <v>20180913892.052</v>
+        <v>20772245353.998</v>
       </c>
       <c r="M8">
-        <v>22336272442.638</v>
+        <v>22911898438.414</v>
       </c>
     </row>
     <row r="9">
@@ -729,40 +729,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>276231.947</v>
+        <v>294258.32</v>
       </c>
       <c r="C9">
-        <v>264210.168</v>
+        <v>281705.058</v>
       </c>
       <c r="D9">
-        <v>288253.73</v>
+        <v>306811.583</v>
       </c>
       <c r="E9">
-        <v>764731.1429999999</v>
+        <v>771185.91</v>
       </c>
       <c r="F9">
-        <v>738791.697</v>
+        <v>745144.5580000001</v>
       </c>
       <c r="G9">
-        <v>790670.5900000001</v>
+        <v>797227.2610000001</v>
       </c>
       <c r="H9">
-        <v>3415367502.208</v>
+        <v>3435410373.305</v>
       </c>
       <c r="I9">
-        <v>3258098597.662</v>
+        <v>3281238736.198</v>
       </c>
       <c r="J9">
-        <v>3572636406.754</v>
+        <v>3589582010.412</v>
       </c>
       <c r="K9">
-        <v>101709242096.286</v>
+        <v>102567725931.762</v>
       </c>
       <c r="L9">
-        <v>98259295775.66899</v>
+        <v>99104226193.76299</v>
       </c>
       <c r="M9">
-        <v>105159188416.902</v>
+        <v>106031225669.762</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/HIA_per_disease_Rubin.xlsx
+++ b/output/Tables/2019/HIA_per_disease_Rubin.xlsx
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>58925.169</v>
+        <v>51358.943</v>
       </c>
       <c r="C2">
-        <v>55995.747</v>
+        <v>48710.419</v>
       </c>
       <c r="D2">
-        <v>61854.592</v>
+        <v>54007.466</v>
       </c>
       <c r="E2">
-        <v>606959.8050000001</v>
+        <v>552337.797</v>
       </c>
       <c r="F2">
-        <v>588962.262</v>
+        <v>535022.8540000001</v>
       </c>
       <c r="G2">
-        <v>624957.348</v>
+        <v>569652.741</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>80725654035.556</v>
+        <v>73460927037.442</v>
       </c>
       <c r="L2">
-        <v>78331980839.765</v>
+        <v>71158039578.248</v>
       </c>
       <c r="M2">
-        <v>83119327231.34801</v>
+        <v>75763814496.636</v>
       </c>
     </row>
     <row r="3">
@@ -471,40 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>40691.563</v>
+        <v>35268.298</v>
       </c>
       <c r="C3">
-        <v>38919.739</v>
+        <v>33607.156</v>
       </c>
       <c r="D3">
-        <v>42463.387</v>
+        <v>36929.44</v>
       </c>
       <c r="E3">
-        <v>36292.19</v>
+        <v>48652.485</v>
       </c>
       <c r="F3">
-        <v>34859.598</v>
+        <v>46570.338</v>
       </c>
       <c r="G3">
-        <v>37724.783</v>
+        <v>50734.631</v>
       </c>
       <c r="H3">
-        <v>2266601445.039</v>
+        <v>1858462975.429</v>
       </c>
       <c r="I3">
-        <v>2167907322.714</v>
+        <v>1770929088.517</v>
       </c>
       <c r="J3">
-        <v>2365295567.364</v>
+        <v>1945996862.341</v>
       </c>
       <c r="K3">
-        <v>4826861303.836</v>
+        <v>6470780491.468</v>
       </c>
       <c r="L3">
-        <v>4636326518.17</v>
+        <v>6193854997.428</v>
       </c>
       <c r="M3">
-        <v>5017396089.503</v>
+        <v>6747705985.508</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>30229.519</v>
+        <v>8198.072</v>
       </c>
       <c r="C4">
-        <v>28895.149</v>
+        <v>7725.354</v>
       </c>
       <c r="D4">
-        <v>31563.89</v>
+        <v>8670.789000000001</v>
       </c>
       <c r="E4">
-        <v>45478.511</v>
+        <v>3858.732</v>
       </c>
       <c r="F4">
-        <v>43018.981</v>
+        <v>3651.919</v>
       </c>
       <c r="G4">
-        <v>47938.04</v>
+        <v>4065.545</v>
       </c>
       <c r="H4">
-        <v>447608494.82</v>
+        <v>240359259.475</v>
       </c>
       <c r="I4">
-        <v>427850468.752</v>
+        <v>226499647.45</v>
       </c>
       <c r="J4">
-        <v>467366520.888</v>
+        <v>254218871.499</v>
       </c>
       <c r="K4">
-        <v>6048641946.477</v>
+        <v>513211387.27</v>
       </c>
       <c r="L4">
-        <v>5721524533.314</v>
+        <v>485705230.245</v>
       </c>
       <c r="M4">
-        <v>6375759359.639</v>
+        <v>540717544.295</v>
       </c>
     </row>
     <row r="5">
@@ -557,40 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>6467.869</v>
+        <v>5754.042</v>
       </c>
       <c r="C5">
-        <v>6182.283</v>
+        <v>5481.703</v>
       </c>
       <c r="D5">
-        <v>6753.455</v>
+        <v>6026.381</v>
       </c>
       <c r="E5">
-        <v>12608.979</v>
+        <v>10356.365</v>
       </c>
       <c r="F5">
-        <v>12026.415</v>
+        <v>9822.546</v>
       </c>
       <c r="G5">
-        <v>13191.543</v>
+        <v>10890.183</v>
       </c>
       <c r="H5">
-        <v>486390218.76</v>
+        <v>225564203.16</v>
       </c>
       <c r="I5">
-        <v>464913885.774</v>
+        <v>214888246.29</v>
       </c>
       <c r="J5">
-        <v>507866551.745</v>
+        <v>236240160.03</v>
       </c>
       <c r="K5">
-        <v>1676994188.187</v>
+        <v>1377396479.914</v>
       </c>
       <c r="L5">
-        <v>1599513135.914</v>
+        <v>1306398587.587</v>
       </c>
       <c r="M5">
-        <v>1754475240.461</v>
+        <v>1448394372.241</v>
       </c>
     </row>
     <row r="6">
@@ -600,40 +600,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>13944.428</v>
+        <v>11679.166</v>
       </c>
       <c r="C6">
-        <v>13098.584</v>
+        <v>10911.866</v>
       </c>
       <c r="D6">
-        <v>14790.271</v>
+        <v>12446.467</v>
       </c>
       <c r="E6">
-        <v>23366.857</v>
+        <v>13312.283</v>
       </c>
       <c r="F6">
-        <v>22207.806</v>
+        <v>12418.34</v>
       </c>
       <c r="G6">
-        <v>24525.908</v>
+        <v>14206.225</v>
       </c>
       <c r="H6">
-        <v>234810214.686</v>
+        <v>194434763.771</v>
       </c>
       <c r="I6">
-        <v>220567058.958</v>
+        <v>181660745.091</v>
       </c>
       <c r="J6">
-        <v>249053370.415</v>
+        <v>207208782.451</v>
       </c>
       <c r="K6">
-        <v>3107791970.082</v>
+        <v>1770533574.597</v>
       </c>
       <c r="L6">
-        <v>2953638210.103</v>
+        <v>1651639167.041</v>
       </c>
       <c r="M6">
-        <v>3261945730.061</v>
+        <v>1889427982.152</v>
       </c>
     </row>
     <row r="7">
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>143999.772</v>
+        <v>126217.175</v>
       </c>
       <c r="C7">
-        <v>138613.556</v>
+        <v>121266.367</v>
       </c>
       <c r="D7">
-        <v>149385.988</v>
+        <v>131167.983</v>
       </c>
       <c r="E7">
-        <v>46479.568</v>
+        <v>47757.797</v>
       </c>
       <c r="F7">
-        <v>44069.496</v>
+        <v>45335.679</v>
       </c>
       <c r="G7">
-        <v>48889.639</v>
+        <v>50179.916</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -670,56 +670,56 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>6181782487.624</v>
+        <v>6351787052.798</v>
       </c>
       <c r="L7">
-        <v>5861242956.497</v>
+        <v>6029645336.884</v>
       </c>
       <c r="M7">
-        <v>6502322018.75</v>
+        <v>6673928768.713</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>Chronic diseases</t>
         </is>
       </c>
       <c r="B8">
-        <v>235333.151</v>
+        <v>60899.578</v>
       </c>
       <c r="C8">
-        <v>225709.311</v>
+        <v>57726.07900000001</v>
       </c>
       <c r="D8">
-        <v>244956.991</v>
+        <v>64073.077</v>
       </c>
       <c r="E8">
-        <v>164226.105</v>
+        <v>76179.86500000001</v>
       </c>
       <c r="F8">
-        <v>156182.296</v>
+        <v>72463.14300000001</v>
       </c>
       <c r="G8">
-        <v>172269.913</v>
+        <v>79896.584</v>
       </c>
       <c r="H8">
-        <v>3435410373.305</v>
+        <v>2518821201.835</v>
       </c>
       <c r="I8">
-        <v>3281238736.198</v>
+        <v>2393977727.348</v>
       </c>
       <c r="J8">
-        <v>3589582010.412</v>
+        <v>2643664676.321001</v>
       </c>
       <c r="K8">
-        <v>21842071896.206</v>
+        <v>10131921933.249</v>
       </c>
       <c r="L8">
-        <v>20772245353.998</v>
+        <v>9637597982.301001</v>
       </c>
       <c r="M8">
-        <v>22911898438.414</v>
+        <v>10626245884.196</v>
       </c>
     </row>
     <row r="9">
@@ -729,40 +729,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>294258.32</v>
+        <v>238475.696</v>
       </c>
       <c r="C9">
-        <v>281705.058</v>
+        <v>227702.865</v>
       </c>
       <c r="D9">
-        <v>306811.583</v>
+        <v>249248.526</v>
       </c>
       <c r="E9">
-        <v>771185.91</v>
+        <v>676275.459</v>
       </c>
       <c r="F9">
-        <v>745144.5580000001</v>
+        <v>652821.676</v>
       </c>
       <c r="G9">
-        <v>797227.2610000001</v>
+        <v>699729.241</v>
       </c>
       <c r="H9">
-        <v>3435410373.305</v>
+        <v>2518821201.835</v>
       </c>
       <c r="I9">
-        <v>3281238736.198</v>
+        <v>2393977727.348</v>
       </c>
       <c r="J9">
-        <v>3589582010.412</v>
+        <v>2643664676.321001</v>
       </c>
       <c r="K9">
-        <v>102567725931.762</v>
+        <v>89944636023.48901</v>
       </c>
       <c r="L9">
-        <v>99104226193.76299</v>
+        <v>86825282897.433</v>
       </c>
       <c r="M9">
-        <v>106031225669.762</v>
+        <v>93063989149.54498</v>
       </c>
     </row>
   </sheetData>
